--- a/data/trans_orig/P5709-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5709-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2007</t>
+          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>331958</t>
+          <t>331796</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>384827</t>
+          <t>384629</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>269159</t>
+          <t>267744</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>320408</t>
+          <t>321645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>616873</t>
+          <t>617101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>690821</t>
+          <t>687610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173404</t>
+          <t>174590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220516</t>
+          <t>222001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>160163</t>
+          <t>158145</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205238</t>
+          <t>205862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346626</t>
+          <t>345614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>413214</t>
+          <t>414613</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96184</t>
+          <t>95550</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>134206</t>
+          <t>135936</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129929</t>
+          <t>129721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>173072</t>
+          <t>173034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>237710</t>
+          <t>236679</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>298078</t>
+          <t>295644</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35198</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40621</t>
+          <t>40575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68232</t>
+          <t>67382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60110</t>
+          <t>59255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96684</t>
+          <t>93632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19523</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>488866</t>
+          <t>487408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>553341</t>
+          <t>555472</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>444331</t>
+          <t>440687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>510016</t>
+          <t>504091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>950152</t>
+          <t>949422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1038749</t>
+          <t>1042345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>216934</t>
+          <t>216812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>272117</t>
+          <t>270665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222446</t>
+          <t>219623</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277927</t>
+          <t>273177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>455388</t>
+          <t>454537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>531914</t>
+          <t>535478</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>130522</t>
+          <t>132576</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>179134</t>
+          <t>178598</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>151334</t>
+          <t>152431</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>200873</t>
+          <t>201124</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>297415</t>
+          <t>294788</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>363827</t>
+          <t>365256</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20689</t>
+          <t>21516</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43809</t>
+          <t>44549</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41259</t>
+          <t>41620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71403</t>
+          <t>71684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67703</t>
+          <t>68415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106344</t>
+          <t>108052</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24318</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16715</t>
+          <t>16495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38032</t>
+          <t>38023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>391554</t>
+          <t>390079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>444922</t>
+          <t>442695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>356633</t>
+          <t>361252</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>406177</t>
+          <t>410605</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>762420</t>
+          <t>765956</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>834713</t>
+          <t>837885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,5%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128276</t>
+          <t>132015</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174122</t>
+          <t>173909</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121048</t>
+          <t>120927</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>164673</t>
+          <t>162220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264154</t>
+          <t>258881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>325154</t>
+          <t>321284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66173</t>
+          <t>65659</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101526</t>
+          <t>100614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>94405</t>
+          <t>93424</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>133752</t>
+          <t>129655</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>168247</t>
+          <t>167633</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>218324</t>
+          <t>220555</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>14755</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34431</t>
+          <t>36017</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30804</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57597</t>
+          <t>57807</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51085</t>
+          <t>51811</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83132</t>
+          <t>83302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>14838</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19131</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>488508</t>
+          <t>488415</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>547054</t>
+          <t>550407</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>491122</t>
+          <t>492704</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>551817</t>
+          <t>555710</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>995931</t>
+          <t>993681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1087628</t>
+          <t>1082740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205874</t>
+          <t>201982</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254204</t>
+          <t>254558</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208581</t>
+          <t>207816</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>262597</t>
+          <t>263395</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>422217</t>
+          <t>428266</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>500912</t>
+          <t>502322</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106807</t>
+          <t>105940</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>146001</t>
+          <t>146358</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>150464</t>
+          <t>146592</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>195623</t>
+          <t>194823</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>264260</t>
+          <t>262696</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>327186</t>
+          <t>328479</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44513</t>
+          <t>45616</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73765</t>
+          <t>74396</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71614</t>
+          <t>71298</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>109535</t>
+          <t>108594</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125176</t>
+          <t>125558</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>175414</t>
+          <t>174011</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30631</t>
+          <t>31038</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21482</t>
+          <t>21849</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45824</t>
+          <t>44747</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1756447</t>
+          <t>1756013</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1863226</t>
+          <t>1875581</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1617248</t>
+          <t>1614821</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1742229</t>
+          <t>1733667</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3406027</t>
+          <t>3412580</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3576341</t>
+          <t>3571202</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>778006</t>
+          <t>774293</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>872461</t>
+          <t>871965</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>755706</t>
+          <t>753543</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>851586</t>
+          <t>857141</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1554904</t>
+          <t>1558852</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1691604</t>
+          <t>1694845</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>439457</t>
+          <t>433464</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>522360</t>
+          <t>513849</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>560723</t>
+          <t>560772</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>655033</t>
+          <t>654217</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1018977</t>
+          <t>1028357</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1141140</t>
+          <t>1154002</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>114706</t>
+          <t>114215</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>160627</t>
+          <t>161478</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>208296</t>
+          <t>208667</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>270106</t>
+          <t>267043</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>333155</t>
+          <t>336162</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>412663</t>
+          <t>412850</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>19872</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41412</t>
+          <t>41489</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>37309</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>67694</t>
+          <t>66541</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>62584</t>
+          <t>62441</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>99646</t>
+          <t>98743</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2012</t>
+          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>404939</t>
+          <t>403144</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>456233</t>
+          <t>454834</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>381089</t>
+          <t>379909</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>432686</t>
+          <t>434172</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>804058</t>
+          <t>796961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>873358</t>
+          <t>876105</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140343</t>
+          <t>141314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186962</t>
+          <t>184927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140775</t>
+          <t>143136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>188059</t>
+          <t>187176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>296343</t>
+          <t>293564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>360821</t>
+          <t>361180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65627</t>
+          <t>65170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100536</t>
+          <t>101056</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59797</t>
+          <t>60775</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>94083</t>
+          <t>95165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>135021</t>
+          <t>134027</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>183924</t>
+          <t>182709</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32426</t>
+          <t>32074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21138</t>
+          <t>21608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44254</t>
+          <t>46283</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40424</t>
+          <t>39218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68799</t>
+          <t>69310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>30743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>521742</t>
+          <t>523341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>587909</t>
+          <t>589808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>507577</t>
+          <t>500457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>570189</t>
+          <t>569112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1044035</t>
+          <t>1049683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1141766</t>
+          <t>1141055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>238894</t>
+          <t>237195</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>295930</t>
+          <t>296331</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244084</t>
+          <t>241628</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302017</t>
+          <t>303763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>497962</t>
+          <t>499082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>580987</t>
+          <t>581679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111242</t>
+          <t>113575</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158089</t>
+          <t>159584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121120</t>
+          <t>122663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166904</t>
+          <t>167715</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>248457</t>
+          <t>248236</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>313884</t>
+          <t>313760</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35048</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66364</t>
+          <t>66233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46926</t>
+          <t>49418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79324</t>
+          <t>81900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91517</t>
+          <t>90383</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133346</t>
+          <t>133322</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26723</t>
+          <t>26769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36270</t>
+          <t>36643</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>430119</t>
+          <t>428062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>485845</t>
+          <t>486155</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>384483</t>
+          <t>387084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>443790</t>
+          <t>442617</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>830934</t>
+          <t>831091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>912609</t>
+          <t>910645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155702</t>
+          <t>156321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203501</t>
+          <t>204789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173309</t>
+          <t>175681</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>224328</t>
+          <t>222916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>339293</t>
+          <t>342178</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410592</t>
+          <t>414303</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70115</t>
+          <t>70264</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107781</t>
+          <t>109943</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>93996</t>
+          <t>94907</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>135388</t>
+          <t>133675</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>177404</t>
+          <t>174442</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>232312</t>
+          <t>230422</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>27759</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24369</t>
+          <t>24408</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49813</t>
+          <t>49361</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39981</t>
+          <t>40325</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70165</t>
+          <t>69354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>21190</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14447</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34793</t>
+          <t>35443</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>461354</t>
+          <t>456878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>521025</t>
+          <t>521992</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>455338</t>
+          <t>457807</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>519319</t>
+          <t>523897</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>930833</t>
+          <t>934855</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1023544</t>
+          <t>1023596</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>270347</t>
+          <t>270866</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>327808</t>
+          <t>326324</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>309154</t>
+          <t>307695</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>371738</t>
+          <t>364989</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>594341</t>
+          <t>592153</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>677356</t>
+          <t>675087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>84814</t>
+          <t>84188</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>126101</t>
+          <t>124348</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126615</t>
+          <t>126613</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>173637</t>
+          <t>172406</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>217953</t>
+          <t>221975</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>281638</t>
+          <t>283465</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29536</t>
+          <t>29281</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55941</t>
+          <t>54584</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35214</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63232</t>
+          <t>60570</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70731</t>
+          <t>67506</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107415</t>
+          <t>105311</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25318</t>
+          <t>23347</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17807</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40211</t>
+          <t>39611</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29678</t>
+          <t>29439</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>56820</t>
+          <t>59840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1874439</t>
+          <t>1872431</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1997831</t>
+          <t>1993946</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1784263</t>
+          <t>1785192</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1909595</t>
+          <t>1907962</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3690581</t>
+          <t>3699695</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3869056</t>
+          <t>3871390</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,6%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>853077</t>
+          <t>856418</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>964149</t>
+          <t>957887</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>915910</t>
+          <t>918166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1023324</t>
+          <t>1023342</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1805639</t>
+          <t>1803661</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1955079</t>
+          <t>1949315</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>371338</t>
+          <t>372159</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>451425</t>
+          <t>453509</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>441174</t>
+          <t>442184</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>523617</t>
+          <t>528689</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>831901</t>
+          <t>841315</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>945433</t>
+          <t>952191</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>107328</t>
+          <t>106076</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>154766</t>
+          <t>153897</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>149225</t>
+          <t>150687</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>205348</t>
+          <t>207336</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>271639</t>
+          <t>269100</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>341990</t>
+          <t>339953</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>53082</t>
+          <t>53110</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>54739</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>89441</t>
+          <t>90205</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>88173</t>
+          <t>87525</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>130923</t>
+          <t>131535</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2016</t>
+          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2016 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>279560</t>
+          <t>284415</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>332220</t>
+          <t>334744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>285549</t>
+          <t>283177</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>336373</t>
+          <t>336714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>580800</t>
+          <t>580681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>652568</t>
+          <t>654324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>200370</t>
+          <t>202383</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>249039</t>
+          <t>249285</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185017</t>
+          <t>186961</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232307</t>
+          <t>235188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>404999</t>
+          <t>402472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>473140</t>
+          <t>470464</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83696</t>
+          <t>85784</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122241</t>
+          <t>123357</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91525</t>
+          <t>88925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129930</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>181756</t>
+          <t>184708</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236848</t>
+          <t>238966</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>22460</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45680</t>
+          <t>44130</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23942</t>
+          <t>22742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47132</t>
+          <t>47859</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50052</t>
+          <t>51603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84202</t>
+          <t>83469</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>27666</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>482005</t>
+          <t>484823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>549938</t>
+          <t>550480</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>484518</t>
+          <t>484636</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>550886</t>
+          <t>550998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>986407</t>
+          <t>990839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1077591</t>
+          <t>1082411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301686</t>
+          <t>301693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>364432</t>
+          <t>363704</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>317045</t>
+          <t>315670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>379338</t>
+          <t>378497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640069</t>
+          <t>641748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>727968</t>
+          <t>726128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>106996</t>
+          <t>108112</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>150659</t>
+          <t>152106</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108493</t>
+          <t>109886</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152381</t>
+          <t>154919</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>229118</t>
+          <t>228758</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>287701</t>
+          <t>289479</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49817</t>
+          <t>49062</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>25453</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51185</t>
+          <t>50796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57611</t>
+          <t>56660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90717</t>
+          <t>91210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28201</t>
+          <t>28722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>246786</t>
+          <t>248893</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>301560</t>
+          <t>304554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>281061</t>
+          <t>281390</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>334841</t>
+          <t>335414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>545500</t>
+          <t>546616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>618314</t>
+          <t>619541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>281802</t>
+          <t>280528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338305</t>
+          <t>334947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>254464</t>
+          <t>249484</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>309041</t>
+          <t>305796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>550889</t>
+          <t>549645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>625934</t>
+          <t>624246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122752</t>
+          <t>121574</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168171</t>
+          <t>164236</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131186</t>
+          <t>133639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>176096</t>
+          <t>180048</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>268265</t>
+          <t>268160</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>329914</t>
+          <t>334020</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>15094</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34161</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>21907</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44762</t>
+          <t>43394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41489</t>
+          <t>41712</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73090</t>
+          <t>71126</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17941</t>
+          <t>16355</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>449290</t>
+          <t>447563</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>514075</t>
+          <t>506017</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>483000</t>
+          <t>484604</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>555480</t>
+          <t>551361</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>949819</t>
+          <t>956033</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1040983</t>
+          <t>1047956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,11%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251850</t>
+          <t>253924</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>307218</t>
+          <t>306843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>269255</t>
+          <t>271470</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>329370</t>
+          <t>331292</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>537537</t>
+          <t>537901</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>620199</t>
+          <t>617251</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>108582</t>
+          <t>109576</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>149270</t>
+          <t>150572</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131064</t>
+          <t>129364</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>179646</t>
+          <t>177563</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>251263</t>
+          <t>249872</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>312050</t>
+          <t>314156</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23676</t>
+          <t>23855</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47181</t>
+          <t>47226</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37406</t>
+          <t>38175</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68716</t>
+          <t>67177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67676</t>
+          <t>67297</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>105646</t>
+          <t>104430</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20552</t>
+          <t>21073</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28145</t>
+          <t>27581</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43220</t>
+          <t>41835</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1524449</t>
+          <t>1515878</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1642815</t>
+          <t>1635741</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1595651</t>
+          <t>1590510</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1714991</t>
+          <t>1713548</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3142014</t>
+          <t>3141413</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3319833</t>
+          <t>3308554</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,81%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1093574</t>
+          <t>1091525</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1203522</t>
+          <t>1206411</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1083391</t>
+          <t>1078345</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1194579</t>
+          <t>1194089</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2203586</t>
+          <t>2203676</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2361357</t>
+          <t>2360722</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>459184</t>
+          <t>455913</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>542790</t>
+          <t>547318</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>499015</t>
+          <t>508910</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>588055</t>
+          <t>599955</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>983639</t>
+          <t>984550</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1110092</t>
+          <t>1114198</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>105464</t>
+          <t>104585</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>150941</t>
+          <t>150859</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>129159</t>
+          <t>129548</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>179619</t>
+          <t>179925</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>246184</t>
+          <t>246596</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>314511</t>
+          <t>313199</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25421</t>
+          <t>25791</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>50097</t>
+          <t>50698</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>30301</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>57405</t>
+          <t>59657</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>60982</t>
+          <t>61898</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>97121</t>
+          <t>100114</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2023</t>
+          <t>Población según la frecuencia de recibir invitaciones para distraerse y salir con otras personas en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>336576</t>
+          <t>334541</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>389764</t>
+          <t>389009</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>328385</t>
+          <t>333159</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>371467</t>
+          <t>372653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>678799</t>
+          <t>677731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>747275</t>
+          <t>749495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141576</t>
+          <t>138914</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184782</t>
+          <t>184416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178578</t>
+          <t>176518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>215217</t>
+          <t>213381</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>327159</t>
+          <t>329517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>384140</t>
+          <t>386862</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60358</t>
+          <t>62342</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94813</t>
+          <t>94001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64829</t>
+          <t>63976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>88164</t>
+          <t>87651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>132433</t>
+          <t>133260</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171658</t>
+          <t>171959</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33607</t>
+          <t>33175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>27290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43033</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46348</t>
+          <t>46048</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70843</t>
+          <t>70791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24170</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36324</t>
+          <t>37238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>615800</t>
+          <t>617278</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>939792</t>
+          <t>988650</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>452116</t>
+          <t>451686</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>505654</t>
+          <t>505502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1093829</t>
+          <t>1088815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1532847</t>
+          <t>1521348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173780</t>
+          <t>134684</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>394344</t>
+          <t>392526</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>274178</t>
+          <t>274054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>322919</t>
+          <t>324016</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>402866</t>
+          <t>400929</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>691535</t>
+          <t>693251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46440</t>
+          <t>43763</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125037</t>
+          <t>123730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104767</t>
+          <t>105854</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137336</t>
+          <t>137917</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>142323</t>
+          <t>143276</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>248288</t>
+          <t>251035</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52129</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34861</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54976</t>
+          <t>55138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53528</t>
+          <t>54069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98029</t>
+          <t>98774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24353</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27457</t>
+          <t>28428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>20041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44442</t>
+          <t>44329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>321145</t>
+          <t>320608</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>382387</t>
+          <t>382458</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>183279</t>
+          <t>197574</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>510141</t>
+          <t>510196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>446683</t>
+          <t>465137</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>859855</t>
+          <t>867238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213840</t>
+          <t>213793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>272463</t>
+          <t>272980</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107215</t>
+          <t>117567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>290773</t>
+          <t>292167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284187</t>
+          <t>281290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>544484</t>
+          <t>541124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69180</t>
+          <t>69278</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110820</t>
+          <t>110381</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39196</t>
+          <t>48176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>123709</t>
+          <t>124193</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>115964</t>
+          <t>117465</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>220142</t>
+          <t>220570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>25194</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>599513</t>
+          <t>559024</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39815</t>
+          <t>40419</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>782064</t>
+          <t>771693</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,25%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>13782</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,7 +13525,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19966</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>516277</t>
+          <t>514861</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>577321</t>
+          <t>576279</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>624380</t>
+          <t>622839</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>750637</t>
+          <t>748740</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1157655</t>
+          <t>1162187</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1303149</t>
+          <t>1311343</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,01%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210679</t>
+          <t>207947</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>263230</t>
+          <t>263076</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>210797</t>
+          <t>221618</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>302578</t>
+          <t>304310</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>445301</t>
+          <t>445558</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>546849</t>
+          <t>545595</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69837</t>
+          <t>68065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>103757</t>
+          <t>103119</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>68288</t>
+          <t>67875</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>104747</t>
+          <t>103979</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>144923</t>
+          <t>145752</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>196284</t>
+          <t>195720</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33910</t>
+          <t>33989</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62715</t>
+          <t>60755</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>30941</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51987</t>
+          <t>51951</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71127</t>
+          <t>70463</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>105419</t>
+          <t>104989</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23246</t>
+          <t>22471</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19954</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37511</t>
+          <t>37109</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33089</t>
+          <t>33855</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54419</t>
+          <t>55372</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1874509</t>
+          <t>1876365</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2344368</t>
+          <t>2355858</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1533078</t>
+          <t>1507353</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2021278</t>
+          <t>2026131</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3533768</t>
+          <t>3561411</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4205288</t>
+          <t>4218684</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,36%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>729483</t>
+          <t>722177</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1036680</t>
+          <t>1033222</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>820636</t>
+          <t>791527</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1072618</t>
+          <t>1065535</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1647481</t>
+          <t>1674024</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2070789</t>
+          <t>2064735</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>266740</t>
+          <t>261195</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>387273</t>
+          <t>388074</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>305451</t>
+          <t>296806</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>412175</t>
+          <t>411038</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>616544</t>
+          <t>617644</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>785218</t>
+          <t>785081</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>91598</t>
+          <t>94014</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>146024</t>
+          <t>145144</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>146005</t>
+          <t>143903</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>948443</t>
+          <t>984368</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>259360</t>
+          <t>260870</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1419957</t>
+          <t>1235703</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>31743</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>58196</t>
+          <t>58451</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>54502</t>
+          <t>53514</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>85884</t>
+          <t>85918</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>91251</t>
+          <t>94315</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>133307</t>
+          <t>137520</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
